--- a/important_mails_2026-04-15.xlsx
+++ b/important_mails_2026-04-15.xlsx
@@ -537,7 +537,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -552,79 +552,21 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
+          <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
+          <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed and shipped your removal
-request (W4mGNrNTVu) to the address you specified before.
-Return Summary:
-Quantity Requested: 1
-Quantity Successfully Shipped: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being shipped, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-5270077-7357030
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1477745830956980</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -636,39 +578,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -691,39 +633,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -747,39 +689,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -794,39 +736,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -842,39 +784,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -886,39 +828,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -938,39 +880,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -988,40 +930,40 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1039,39 +981,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -1091,39 +1033,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -1144,39 +1086,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -1197,40 +1139,40 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -1246,39 +1188,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -1297,40 +1239,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -1344,40 +1286,40 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -1395,39 +1337,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -1460,39 +1402,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -1507,39 +1449,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1558,39 +1500,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -1609,39 +1551,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -1653,39 +1595,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -1701,39 +1643,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -1745,39 +1687,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1792,39 +1734,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1845,39 +1787,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1900,39 +1842,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -1948,39 +1890,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -2000,39 +1942,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -2048,6 +1990,64 @@
  To change your email preferences visit: Notification Preferences
  Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
  Amazon EU S.à</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed and shipped your removal
+request (W4mGNrNTVu) to the address you specified before.
+Return Summary:
+Quantity Requested: 1
+Quantity Successfully Shipped: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being shipped, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-5270077-7357030
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1477745830956980</t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-04-15.xlsx
+++ b/important_mails_2026-04-15.xlsx
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1051,176 +1051,21 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
+          <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>EU and UK Compliance Brief</t>
+          <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe
- 96
- EU and UK Compliance Brief
- To better support your compliance journey, we've prepared an overview of regulations that affect your business in Amazon’s European stores. For more information on all compliance requirements, go to
- European compliance requirements
- Country of Origin (COO), EU &amp; UK
- Am I impacted?
- Yes, if you ship across borders to customers:
- - From outside the EU into the EU through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
- - From outside the UK into the UK through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
- Consequences of not meeting the requirement:
- To avoid disruptions to your business, provide this information to your listings by June 30, 2026.
- How do I become compliant?
- You can use the Category Listings Report (CLR) to update the COO information for your existing product listings in bulk:
-- Download the CLR from the “Inventory Reports” page on Seller Central
-- Edit the Country of Origin column for all your produ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>EU and UK Compliance Brief</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe
- 96
- EU and UK Compliance Brief
- To better support your compliance journey, we've prepared an overview of regulations that affect your business in Amazon’s European stores. For more information on all compliance requirements, go to
- European compliance requirements
- Country of Origin (COO), EU &amp; UK
- Am I impacted?
- Yes, if you ship across borders to customers:
- - From outside the EU into the EU through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
- - From outside the UK into the UK through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
- Consequences of not meeting the requirement:
- To avoid disruptions to your business, provide this information to your listings by June 30, 2026.
- How do I become compliant?
- You can use the Category Listings Report (CLR) to update the COO information for your existing product listings in bulk:
-- Download the CLR from the “Inventory Reports” page on Seller Central
-- Edit the Country of Origin column for all your produ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>VAT Calculation Services will calculate VAT by shipment as of June
- 1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>96
- New tax calculation method ensures compliance with European e-invoicing mandates.
- Hello,
- Effective as of June 1, 2026, we’re updating Value Added Tax (VAT) Calculation Services (VCS) to comply with European e-invoicing mandates. Instead of calculating VAT per unit, VCS will calculate VAT on the total invoice amount by tax rate. This means when customers buy multiple units, the total invoice amounts may differ from current calculations.
- Depending on the sales channel (regardless of customer VAT registration), VCS will apply one of two methods:
-- Consumer website : VCS will impute VAT from the VAT-inclusive price. If multiple units are purchased, unit exclusive prices may vary.
-- Amazon Business website : VCS will derive the VAT-exclusive unit price from the VAT-inclusive unit price. VAT will be calculated on the total VAT-exclusive price by tax rate. For more information about invoice-total VAT calculations and to view examples, go to section 10: Invoice-total VAT calculation method of VAT Calculation Services methodology .
- The Amazon Europe team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notific</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 12354633592] 其他账户问题</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -1239,40 +1084,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -1286,40 +1131,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -1337,39 +1182,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -1402,39 +1247,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -1449,39 +1294,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1500,39 +1345,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -1551,39 +1396,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -1595,39 +1440,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -1643,39 +1488,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -1687,86 +1532,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Votre paiement est en cours</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 04/08/26 15:00 CEST, nous avons effectué un virement d’un montant de €
- 26.11 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pé</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1787,39 +1585,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1842,39 +1640,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -1890,39 +1688,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -1942,39 +1740,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -1993,39 +1791,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2051,39 +1849,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2104,39 +1902,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2162,39 +1960,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2214,40 +2012,40 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2263,39 +2061,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2315,39 +2113,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2373,39 +2171,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2421,39 +2219,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2474,39 +2272,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2520,39 +2318,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2566,40 +2364,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -2616,39 +2414,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2668,39 +2466,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2717,39 +2515,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2772,39 +2570,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2824,39 +2622,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2873,39 +2671,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2922,39 +2720,194 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>EU and UK Compliance Brief</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe
+ 96
+ EU and UK Compliance Brief
+ To better support your compliance journey, we've prepared an overview of regulations that affect your business in Amazon’s European stores. For more information on all compliance requirements, go to
+ European compliance requirements
+ Country of Origin (COO), EU &amp; UK
+ Am I impacted?
+ Yes, if you ship across borders to customers:
+ - From outside the EU into the EU through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
+ - From outside the UK into the UK through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
+ Consequences of not meeting the requirement:
+ To avoid disruptions to your business, provide this information to your listings by June 30, 2026.
+ How do I become compliant?
+ You can use the Category Listings Report (CLR) to update the COO information for your existing product listings in bulk:
+- Download the CLR from the “Inventory Reports” page on Seller Central
+- Edit the Country of Origin column for all your produ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>EU and UK Compliance Brief</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe
+ 96
+ EU and UK Compliance Brief
+ To better support your compliance journey, we've prepared an overview of regulations that affect your business in Amazon’s European stores. For more information on all compliance requirements, go to
+ European compliance requirements
+ Country of Origin (COO), EU &amp; UK
+ Am I impacted?
+ Yes, if you ship across borders to customers:
+ - From outside the EU into the EU through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
+ - From outside the UK into the UK through FBA Export programs (Amazon’s global program, FBA Export, Remote Fulfilment with Fulfilment by Amazon) or MFN Exports programs (Fulfilled by Merchant Export)
+ Consequences of not meeting the requirement:
+ To avoid disruptions to your business, provide this information to your listings by June 30, 2026.
+ How do I become compliant?
+ You can use the Category Listings Report (CLR) to update the COO information for your existing product listings in bulk:
+- Download the CLR from the “Inventory Reports” page on Seller Central
+- Edit the Country of Origin column for all your produ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>VAT Calculation Services will calculate VAT by shipment as of June
+ 1</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>96
+ New tax calculation method ensures compliance with European e-invoicing mandates.
+ Hello,
+ Effective as of June 1, 2026, we’re updating Value Added Tax (VAT) Calculation Services (VCS) to comply with European e-invoicing mandates. Instead of calculating VAT per unit, VCS will calculate VAT on the total invoice amount by tax rate. This means when customers buy multiple units, the total invoice amounts may differ from current calculations.
+ Depending on the sales channel (regardless of customer VAT registration), VCS will apply one of two methods:
+- Consumer website : VCS will impute VAT from the VAT-inclusive price. If multiple units are purchased, unit exclusive prices may vary.
+- Amazon Business website : VCS will derive the VAT-exclusive unit price from the VAT-inclusive unit price. VAT will be calculated on the total VAT-exclusive price by tax rate. For more information about invoice-total VAT calculations and to view examples, go to section 10: Invoice-total VAT calculation method of VAT Calculation Services methodology .
+ The Amazon Europe team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notific</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -2977,39 +2930,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3027,39 +2980,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3077,39 +3030,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3129,39 +3082,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3179,39 +3132,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3229,39 +3182,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3279,39 +3232,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3326,39 +3279,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3376,39 +3329,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3426,39 +3379,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3476,39 +3429,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3523,39 +3476,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3570,39 +3523,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3617,39 +3570,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3668,40 +3621,40 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3720,39 +3673,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3762,39 +3715,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3812,39 +3765,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3857,6 +3810,53 @@
  https://sellercentral.amazon.ca/performance/account/health/compliance-request
 If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
 If you are not the correct point of contact, please re-direct this email to the correct point of contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Votre paiement est en cours</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Félicitations ! Votre paiement est en cours et arrivera sous peu.
+ Tentative de versement
+Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
+Le 04/08/26 15:00 CEST, nous avons effectué un virement d’un montant de €
+ 26.11 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
+ Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
+ Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
+ Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pé</t>
         </is>
       </c>
     </row>
